--- a/reports/빅딜/history/2026-09-25/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-09-25/빅딜_league_mgf_report.xlsx
@@ -123,7 +123,7 @@
     <t>5경 985조 128억 1537만</t>
   </si>
   <si>
-    <t>셀린느2군 IN 300위분들   귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -222,7 +222,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8188조 1,046억 1,273만</t>
+    <t>8188조 1046억 1273만</t>
   </si>
   <si>
     <t>2</t>
@@ -240,7 +240,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>6992조 3,764억 4,633만</t>
+    <t>6992조 3764억 4633만</t>
   </si>
   <si>
     <t>3</t>
@@ -255,7 +255,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>4402조 1,032억 4,015만</t>
+    <t>4402조 1032억 4015만</t>
   </si>
   <si>
     <t>4</t>
@@ -273,7 +273,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4094조 124억 4,985만</t>
+    <t>4094조 124억 4985만</t>
   </si>
   <si>
     <t>5</t>
@@ -288,7 +288,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>3303조 6,174억 3,840만</t>
+    <t>3303조 6174억 3840만</t>
   </si>
   <si>
     <t>6</t>
@@ -303,7 +303,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>2988조 9,066억 1,886만</t>
+    <t>2988조 9066억 1886만</t>
   </si>
   <si>
     <t>7</t>
@@ -318,7 +318,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2424조 9,978억 2,159만</t>
+    <t>2424조 9978억 2159만</t>
   </si>
   <si>
     <t>8</t>
@@ -333,37 +333,37 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>2269조 6,121억 182만</t>
+    <t>2290조 8654억 1226만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2279조 9226억 7885만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>지존빼앙</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2224조 5,091억 9,296만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>2182조 5,730억 5,749만</t>
+    <t>2224조 5091억 9296만</t>
   </si>
   <si>
     <t>11</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>1978조 8,306억 8,833만</t>
+    <t>1978조 8306억 8833만</t>
   </si>
   <si>
     <t>12</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1831조 4,812억 8,418만</t>
+    <t>1831조 4812억 8418만</t>
   </si>
   <si>
     <t>13</t>
@@ -402,7 +402,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>1814조 2,226억 6,845만</t>
+    <t>1814조 2226억 6845만</t>
   </si>
   <si>
     <t>14</t>
@@ -414,7 +414,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1766조 7,006억 9,923만</t>
+    <t>1766조 7006억 9923만</t>
   </si>
   <si>
     <t>15</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1596조 5,749억 9,080만</t>
+    <t>1596조 5749억 9080만</t>
   </si>
   <si>
     <t>16</t>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1240조 6,809억 9,149만</t>
+    <t>1240조 6809억 9149만</t>
   </si>
   <si>
     <t>17</t>
@@ -450,7 +450,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>1213조 7,003억 6,444만</t>
+    <t>1213조 7003억 6444만</t>
   </si>
   <si>
     <t>18</t>
@@ -465,7 +465,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1149조 8,047억 287만</t>
+    <t>1149조 8047억 287만</t>
   </si>
   <si>
     <t>19</t>
@@ -477,7 +477,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1091조 9,888억 5,564만</t>
+    <t>1091조 9888억 5564만</t>
   </si>
   <si>
     <t>20</t>
@@ -489,7 +489,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1050조 4,181억 3,112만</t>
+    <t>1050조 4181억 3112만</t>
   </si>
   <si>
     <t>21</t>
@@ -501,7 +501,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1046조 865억 5,975만</t>
+    <t>1046조 865억 5975만</t>
   </si>
   <si>
     <t>22</t>
@@ -513,7 +513,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1033조 7,202억 5,586만</t>
+    <t>1033조 7202억 5586만</t>
   </si>
   <si>
     <t>23</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1015조 5,704억 3,498만</t>
+    <t>1015조 5704억 3498만</t>
   </si>
   <si>
     <t>24</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>799조 5,234억 8,229만</t>
+    <t>799조 5234억 8229만</t>
   </si>
   <si>
     <t>25</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>796조 5,685억 5,174만</t>
+    <t>796조 5685억 5174만</t>
   </si>
   <si>
     <t>26</t>
@@ -564,7 +564,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>765조 9,289억 1,162만</t>
+    <t>765조 9289억 1162만</t>
   </si>
   <si>
     <t>27</t>
@@ -576,7 +576,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>747조 6,533억 1,496만</t>
+    <t>747조 6533억 1496만</t>
   </si>
   <si>
     <t>28</t>
@@ -588,7 +588,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>665조 2,579억 6,198만</t>
+    <t>665조 2579억 6198만</t>
   </si>
   <si>
     <t>29</t>
@@ -603,7 +603,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>649조 5,527억 6,316만</t>
+    <t>649조 5527억 6316만</t>
   </si>
   <si>
     <t>30</t>
@@ -615,7 +615,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
   </si>
   <si>
-    <t>277조 36억 4,103만</t>
+    <t>277조 36억 4103만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -624,7 +624,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>9713조 4,850억 8,781만</t>
+    <t>9713조 4850억 8781만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -633,7 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>6465조 5,267억 4,688만</t>
+    <t>6465조 5267억 4688만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -642,7 +642,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>3686조 3,442억 6,715만</t>
+    <t>3686조 3442억 6715만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -651,7 +651,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3586조 4,643억 9,612만</t>
+    <t>3586조 4643억 9612만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -660,7 +660,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3469조 8,887억 4,598만</t>
+    <t>3469조 8887억 4598만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2483조 8,452억 3,773만</t>
+    <t>2483조 8452억 3773만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -678,7 +678,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2417조 4,217억 703만</t>
+    <t>2431조 544억 4930만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -687,13 +687,13 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1905조 4,587억 3,879만</t>
+    <t>1905조 4587억 3879만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>1831조 3,912억 3,225만</t>
+    <t>1831조 3912억 3225만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -705,7 +705,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>1825조 2,398억 5,085만</t>
+    <t>1825조 2398억 5085만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -714,7 +714,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>1697조 755억 7,134만</t>
+    <t>1697조 755억 7134만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -726,7 +726,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1259조 8,128억 5,685만</t>
+    <t>1259조 8128억 5685만</t>
   </si>
   <si>
     <t>우후</t>
@@ -735,7 +735,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1058조 2,431억 2,633만</t>
+    <t>1058조 2431억 2633만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -744,7 +744,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1052조 9,891억 7,693만</t>
+    <t>1052조 9891억 7693만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -753,7 +753,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1006조 7,349억 1,730만</t>
+    <t>1006조 7349억 1730만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -762,7 +762,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>987조 2,843억 9,824만</t>
+    <t>987조 2843억 9824만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -771,7 +771,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>926조 2,055억 4,066만</t>
+    <t>928조 8138억 6047만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -780,7 +780,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>914조 9,534억 4,237만</t>
+    <t>914조 9534억 4237만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -789,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>864조 6,290억 5,998만</t>
+    <t>864조 6290억 5998만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -798,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>560조 1,285억 7,637만</t>
+    <t>560조 1285억 7637만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -807,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>532조 1,581억 8,976만</t>
+    <t>532조 1581억 8976만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -816,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>459조 5,489억 3,382만</t>
+    <t>459조 5489억 3382만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -825,7 +825,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>420조 8,785억 9,592만</t>
+    <t>420조 8785억 9592만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -834,7 +834,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>410조 5,852억 7,919만</t>
+    <t>410조 5852억 7919만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -843,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>372조 4,821억 9,681만</t>
+    <t>372조 4821억 9681만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -852,7 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
   </si>
   <si>
-    <t>275조 6,869억 3,523만</t>
+    <t>275조 6869억 3523만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>249조 9,325억 1,140만</t>
+    <t>249조 9325억 1140만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -873,7 +873,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>245조 4,859억 3,395만</t>
+    <t>245조 4859억 3395만</t>
   </si>
   <si>
     <t>가겠습니다</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>7363조 6,456억 7,965만</t>
+    <t>7363조 6456억 7965만</t>
   </si>
   <si>
     <t>라카도</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4712조 790억 3,428만</t>
+    <t>4712조 790억 3428만</t>
   </si>
   <si>
     <t>롤대신해야지</t>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
   </si>
   <si>
-    <t>3728조 6,519억 2,880만</t>
+    <t>3728조 6519억 2880만</t>
   </si>
   <si>
     <t>미우맘</t>
@@ -909,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
   </si>
   <si>
-    <t>3003조 1,592억 9,722만</t>
+    <t>3003조 1592억 9722만</t>
   </si>
   <si>
     <t>개종망겜</t>
@@ -918,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
   </si>
   <si>
-    <t>2774조 2,722억 1,106만</t>
+    <t>2774조 2722억 1106만</t>
   </si>
   <si>
     <t>커튼월</t>
@@ -927,7 +927,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>2479조 6,616억 3,099만</t>
+    <t>2479조 6616억 3099만</t>
   </si>
   <si>
     <t>gorystalLOVE</t>
@@ -936,7 +936,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
   </si>
   <si>
-    <t>2290조 9,695억 1,564만</t>
+    <t>2290조 9695억 1564만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -945,7 +945,7 @@
     <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
   </si>
   <si>
-    <t>2274조 2,104억 2,874만</t>
+    <t>2274조 2104억 2874만</t>
   </si>
   <si>
     <t>명지동꿀주먹</t>
@@ -954,7 +954,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>2258조 2,854억 4,445만</t>
+    <t>2258조 2854억 4445만</t>
   </si>
   <si>
     <t>Judge99</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=Judge99</t>
   </si>
   <si>
-    <t>2185조 696억 5,500만</t>
+    <t>2185조 696억 5500만</t>
   </si>
   <si>
     <t>천요화</t>
@@ -972,13 +972,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
   </si>
   <si>
-    <t>2161조 3,214억 2,617만</t>
+    <t>2161조 3214억 2617만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
   </si>
   <si>
-    <t>2102조 5,589억 5,859만</t>
+    <t>2102조 5589억 5859만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -987,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1400조 5,111억 4,442만</t>
+    <t>1400조 5111억 4442만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -996,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1028조 843억 4,082만</t>
+    <t>1028조 843억 4082만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -1005,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
   </si>
   <si>
-    <t>965조 5,474억 7,452만</t>
+    <t>965조 5474억 7452만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -1014,7 +1014,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>951조 7,711억 3,126만</t>
+    <t>951조 7711억 3126만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -1023,7 +1023,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
   </si>
   <si>
-    <t>923조 9,124억 9,450만</t>
+    <t>923조 9124억 9450만</t>
   </si>
   <si>
     <t>양룽</t>
@@ -1032,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
   </si>
   <si>
-    <t>867조 2,556억 5,423만</t>
+    <t>867조 2556억 5423만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -1041,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
   </si>
   <si>
-    <t>847조 3,200억 1,616만</t>
+    <t>847조 3200억 1616만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1050,7 +1050,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>738조 8,419억 1,124만</t>
+    <t>738조 8419억 1124만</t>
   </si>
   <si>
     <t>욧츠</t>
@@ -1059,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
   </si>
   <si>
-    <t>732조 6,506억 5,328만</t>
+    <t>732조 6506억 5328만</t>
   </si>
   <si>
     <t>gorystal</t>
@@ -1068,7 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>715조 4,194억 1,453만</t>
+    <t>715조 4194억 1453만</t>
   </si>
   <si>
     <t>복룽</t>
@@ -1077,7 +1077,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>710조 5,967억 7,854만</t>
+    <t>710조 5967억 7854만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1086,7 +1086,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
   </si>
   <si>
-    <t>657조 7,522억 2,440만</t>
+    <t>657조 7522억 2440만</t>
   </si>
   <si>
     <t>뀨꾸룽</t>
@@ -1095,7 +1095,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
   </si>
   <si>
-    <t>656조 7,617억 4,920만</t>
+    <t>656조 7617억 4920만</t>
   </si>
   <si>
     <t>짜상무</t>
@@ -1104,7 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
   </si>
   <si>
-    <t>642조 9,928억 6,971만</t>
+    <t>642조 9928억 6971만</t>
   </si>
   <si>
     <t>률율율</t>
@@ -1113,7 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>547조 1,538억 8,441만</t>
+    <t>547조 1538억 8441만</t>
   </si>
   <si>
     <t>매리골드</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>389조 9,183억 6,640만</t>
+    <t>389조 9183억 6640만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -1131,7 +1131,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>372조 7,777억 7,671만</t>
+    <t>372조 7777억 7671만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1140,13 +1140,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>334조 1,776억 1,349만</t>
+    <t>334조 1776억 1349만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>5731조 3,781억 8,495만</t>
+    <t>5731조 3781억 8495만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1155,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
   </si>
   <si>
-    <t>5708조 2,885억 4,200만</t>
+    <t>5708조 2885억 4200만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -1164,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>3802조 2,509억 9,228만</t>
+    <t>3802조 2509억 9228만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3347조 9,436억 1,500만</t>
+    <t>3347조 9436억 1500만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1182,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2706조 7,527억 6,350만</t>
+    <t>2706조 7527억 6350만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -1191,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2216조 4,022억 554만</t>
+    <t>2216조 4022억 554만</t>
   </si>
   <si>
     <t>여니워니</t>
@@ -1200,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
   </si>
   <si>
-    <t>2210조 5,639억 7,060만</t>
+    <t>2210조 5639억 7060만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>2204조 873억 8,415만</t>
+    <t>2204조 873억 8415만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1218,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>2094조 3,509억 5,174만</t>
+    <t>2094조 3509억 5174만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
   </si>
   <si>
-    <t>1842조 5,559억 6,212만</t>
+    <t>1842조 5559억 6212만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1236,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1733조 9,308억 7,806만</t>
+    <t>1733조 9308억 7806만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1245,7 +1245,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>1649조 581억 7,955만</t>
+    <t>1649조 581억 7955만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1254,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>1643조 4,872억 6,754만</t>
+    <t>1643조 4872억 6754만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1263,7 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
   </si>
   <si>
-    <t>1532조 7,337억 2,070만</t>
+    <t>1532조 7337억 2070만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1272,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1451조 9,418억 545만</t>
+    <t>1451조 9418억 545만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1281,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1319조 5,858억 7,337만</t>
+    <t>1319조 5858억 7337만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1290,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1098조 1,848억 4,864만</t>
+    <t>1098조 1848억 4864만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1299,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>925조 8,925억 1,529만</t>
+    <t>925조 8925억 1529만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1308,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>902조 2,941억 6,618만</t>
+    <t>902조 2941억 6618만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>884조 6,876억 1,268만</t>
+    <t>884조 6876억 1268만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>881조 2,976억 2,492만</t>
+    <t>881조 2976억 2492만</t>
   </si>
   <si>
     <t>박금쪽</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
   </si>
   <si>
-    <t>804조 4,549억 516만</t>
+    <t>804조 4549억 516만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1344,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>738조 7,041억 4,433만</t>
+    <t>738조 7041억 4433만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1353,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>737조 1,909억 7,080만</t>
+    <t>737조 1909억 7080만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1362,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
   </si>
   <si>
-    <t>725조 7,659억 853만</t>
+    <t>725조 7659억 853만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1371,7 +1371,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
   </si>
   <si>
-    <t>627조 1,553억 6,314만</t>
+    <t>627조 1553억 6314만</t>
   </si>
   <si>
     <t>계니규니</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>563조 6,801억 7,647만</t>
+    <t>563조 6801억 7647만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1389,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>448조 4,913억 2,823만</t>
+    <t>448조 4913억 2823만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>368조 1,032억 9,070만</t>
+    <t>368조 1032억 9070만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1407,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>310조 1,700억 7,637만</t>
+    <t>310조 1700억 7637만</t>
   </si>
 </sst>
 </file>
@@ -2014,7 +2014,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2326,13 +2326,13 @@
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2343,25 +2343,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>112</v>
@@ -2390,7 +2390,7 @@
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>81</v>
@@ -2553,7 +2553,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>137</v>
@@ -2585,7 +2585,7 @@
         <v>101</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>141</v>
@@ -2649,7 +2649,7 @@
         <v>101</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>150</v>
@@ -2713,7 +2713,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
@@ -2745,7 +2745,7 @@
         <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>162</v>
@@ -2809,7 +2809,7 @@
         <v>124</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>170</v>
@@ -2937,7 +2937,7 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>187</v>
@@ -2969,7 +2969,7 @@
         <v>191</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>192</v>
@@ -3058,7 +3058,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3181,7 +3181,7 @@
         <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>205</v>
@@ -3373,7 +3373,7 @@
         <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>222</v>
@@ -3387,7 +3387,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>223</v>
@@ -3405,7 +3405,7 @@
         <v>225</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>226</v>
@@ -3469,7 +3469,7 @@
         <v>232</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>233</v>
@@ -3565,7 +3565,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>242</v>
@@ -3597,7 +3597,7 @@
         <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>245</v>
@@ -3658,7 +3658,7 @@
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>178</v>
@@ -3693,7 +3693,7 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>254</v>
@@ -4037,7 +4037,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4125,7 +4125,7 @@
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>64</v>
@@ -4366,7 +4366,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>310</v>
@@ -4480,7 +4480,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>320</v>
@@ -4512,7 +4512,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>323</v>
@@ -4544,7 +4544,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>326</v>
@@ -4573,7 +4573,7 @@
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>145</v>
@@ -4605,7 +4605,7 @@
         <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>96</v>
@@ -4640,7 +4640,7 @@
         <v>101</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>335</v>
@@ -4704,7 +4704,7 @@
         <v>69</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>341</v>
@@ -4736,7 +4736,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>344</v>
@@ -4768,7 +4768,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>347</v>
@@ -4800,7 +4800,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>350</v>
@@ -4864,7 +4864,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>356</v>
@@ -4992,7 +4992,7 @@
         <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>368</v>
@@ -5021,7 +5021,7 @@
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>178</v>
@@ -5082,7 +5082,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5138,7 +5138,7 @@
         <v>140</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>70</v>
@@ -5365,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>394</v>
@@ -5411,7 +5411,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>398</v>
@@ -5554,10 +5554,10 @@
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>412</v>
@@ -5621,7 +5621,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>418</v>
@@ -5714,10 +5714,10 @@
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>427</v>
@@ -5749,7 +5749,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>430</v>
@@ -5973,7 +5973,7 @@
         <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>451</v>
